--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Winding down after a long day in the field.</t>
+          <t>Night falls over the hive.</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Night falls over the hive.</t>
+          <t>The comb quietens as the stars come out.</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>The comb quietens as the stars come out.</t>
+          <t>Just one more game... famous last words in the hive.</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 9:00 PM and midnight local time.</t>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>Just one more game... famous last words in the hive.</t>
+          <t>Morning in the comb — the day's first harvest begins!</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Morning in the comb — the day's first harvest begins!</t>
+          <t>Peak pollen-gathering hours!</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Peak pollen-gathering hours!</t>
+          <t>The hive is buzzing with morning energy.</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>The hive is buzzing with morning energy.</t>
+          <t>High noon in the hive — time for a honey break!</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>High noon in the hive — time for a honey break!</t>
+          <t>The sun is high, and the nectar is sweet.</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>The sun is high, and the nectar is sweet.</t>
+          <t>Midday match! A quick break between flights.</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Midday match! A quick break between flights.</t>
+          <t>Golden afternoon light fills the comb.</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>Golden afternoon light fills the comb.</t>
+          <t>The afternoon warmth has the bees buzzing lively.</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>The afternoon warmth has the bees buzzing lively.</t>
+          <t>Basking in the warm afternoon sun.</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Basking in the warm afternoon sun.</t>
+          <t>The sun sets over the hive — time for evening games.</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>The sun sets over the hive — time for evening games.</t>
+          <t>Workers return home after a full day's buzz.</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Workers return home after a full day's buzz.</t>
+          <t>Golden hour in the honeycomb.</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -2226,27 +2226,27 @@
       </c>
     </row>
     <row r="38" ht="14.6" customHeight="1" s="8">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>Golden hour in the honeycomb.</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>On Game Load</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Warming up flights muscles…</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Warming up flights muscles…</t>
+          <t>Pollinating the processors…</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Pollinating the processors…</t>
+          <t>Untangling waggle-dance choreography…</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Untangling waggle-dance choreography…</t>
+          <t>Generating royal jelly…</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Generating royal jelly…</t>
+          <t>Sealing the honeycomb…</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Sealing the honeycomb…</t>
+          <t>Consulting the Queen Bee…</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Consulting the Queen Bee…</t>
+          <t>Calibrating stingers…</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Calibrating stingers…</t>
+          <t>Deploying scout bees…</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Deploying scout bees…</t>
+          <t>Counting the worker bees…</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Counting the worker bees…</t>
+          <t>Preparing a sticky situation…</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Preparing a sticky situation…</t>
+          <t>The swarm is gathering…</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>The swarm is gathering…</t>
+          <t>Sweeping the hive…</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Sweeping the hive…</t>
+          <t>Gathering nectar from local memory…</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Gathering nectar from local memory…</t>
+          <t>Guarding the entrance from wasps…</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Guarding the entrance from wasps…</t>
+          <t>Feeding the larvae bits and bytes…</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Feeding the larvae bits and bytes…</t>
+          <t>Orienting new forager bees…</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Orienting new forager bees…</t>
+          <t>Cross-referencing pollen routes…</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Cross-referencing pollen routes…</t>
+          <t>Recruiting nurse bees…</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Recruiting nurse bees…</t>
+          <t>Loading nectar reserves…</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Loading nectar reserves…</t>
+          <t>Synchronizing with the hive mind…</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>Synchronizing with the hive mind…</t>
+          <t>Tuning antennae for reception…</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Tuning antennae for reception…</t>
+          <t>Propolis-sealing the cracks…</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Propolis-sealing the cracks…</t>
+          <t>Rousing drones from their nap…</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2849,27 +2849,27 @@
     <row r="61" ht="14.6" customHeight="1" s="8">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B61" s="5" t="inlineStr">
-        <is>
-          <t>On Game Load</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Rousing drones from their nap…</t>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>The hive hums quietly, waiting for your next move.</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>Loading</t>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Toast</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>The hive hums quietly, waiting for your next move.</t>
+          <t>A stray bee drifts across the board...</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>A stray bee drifts across the board...</t>
+          <t>It’s when you can’t hear the bees, that’s when the bees are coming.</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>It’s when you can’t hear the bees, that’s when the bees are coming.</t>
+          <t>Somewhere, honey is dripping.</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Somewhere, honey is dripping.</t>
+          <t>The comb creaks softly under the weight of gathered honey.</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>The comb creaks softly under the weight of gathered honey.</t>
+          <t>A distant hum grows louder... or is that just the board?</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>A distant hum grows louder... or is that just the board?</t>
+          <t>Pollen settles on the board like fine snow.</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -3046,12 +3046,12 @@
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Pollen settles on the board like fine snow.</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>Somewhere, a queen bee hums a low, satisfied note.</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Somewhere, a queen bee hums a low, satisfied note.</t>
+          <t>The board glows faintly gold in the afternoon light.</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>The board glows faintly gold in the afternoon light.</t>
+          <t>A single petal drifts down onto the comb.</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>A single petal drifts down onto the comb.</t>
+          <t>The hive never truly sleeps.</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -3154,12 +3154,12 @@
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>The hive never truly sleeps.</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>The swarm is silently judging your strategy.</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
@@ -3181,9 +3181,9 @@
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>The swarm is silently judging your strategy.</t>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>A worker bee pauses mid-flight, unsure why.</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>A worker bee pauses mid-flight, unsure why.</t>
+          <t>Somewhere, a bee is telling the others where you’ve been.</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Somewhere, a bee is telling the others where you’ve been.</t>
+          <t>The hive remembers every card you’ve touched.</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>The hive remembers every card you’ve touched.</t>
+          <t>Nothing moves. Everything hums.</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Nothing moves. Everything hums.</t>
+          <t>The edges of the cards are getting a little sticky.</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>The edges of the cards are getting a little sticky.</t>
+          <t>The bees are keeping score. They always do.</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>The bees are keeping score. They always do.</t>
+          <t>A bee lands, looks around, and leaves again.</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>A bee lands, looks around, and leaves again.</t>
+          <t>The hum has changed pitch. Did you notice?</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>The hum has changed pitch. Did you notice?</t>
+          <t>Time moves differently inside the comb.</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Time moves differently inside the comb.</t>
+          <t>Somewhere, wax is being warmed by tiny bodies.</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Somewhere, wax is being warmed by tiny bodies.</t>
+          <t>Even idle hands make honey eventually.</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Even idle hands make honey eventually.</t>
+          <t>The bees are patient. Are you?</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>The bees are patient. Are you?</t>
+          <t>The hive keeps its own time.</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3524,52 +3524,52 @@
     <row r="86" ht="14.6" customHeight="1" s="8">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Idle Action</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>No action taken for one minute.</t>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>3+ Hints used in one match.</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>The hive keeps its own time.</t>
-        </is>
-      </c>
-      <c r="D86" s="4" t="inlineStr">
-        <is>
-          <t>Ambiance</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
+          <t>Need a little help? The scout bees are buzzing suggestions.</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="87" ht="14.6" customHeight="1" s="8">
-      <c r="A87" s="5" t="inlineStr">
+      <c r="A87" s="1" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="1" t="inlineStr">
         <is>
           <t>3+ Hints used in one match.</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Need a little help? The scout bees are buzzing suggestions.</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Waggle dance activated!</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E87" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>Waggle dance activated!</t>
+          <t>The bees checked every flower!</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>The bees checked every flower!</t>
+          <t>The hive mind is thinking...</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>The hive mind is thinking...</t>
+          <t>The hive has reached a consensus.</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>The hive has reached a consensus.</t>
+          <t>Even the busiest bees ask the Queen for directions sometimes.</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Even the busiest bees ask the Queen for directions sometimes.</t>
+          <t>A drop of honey marks a sweet path forward.</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>A drop of honey marks a sweet path forward.</t>
+          <t>Nectar trail spotted! Follow this lead.</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>Nectar trail spotted! Follow this lead.</t>
+          <t>A little bee whispered a suggestion in your ear.</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr">
@@ -3765,54 +3765,54 @@
       </c>
     </row>
     <row r="95" ht="14.6" customHeight="1" s="8">
-      <c r="A95" s="1" t="inlineStr">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>3+ Hints used in one match.</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>A little bee whispered a suggestion in your ear.</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Undo used immediately after a placement.</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Second thoughts? Wise bees always double-check.</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="96" ht="14.6" customHeight="1" s="8">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="A96" s="1" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="1" t="inlineStr">
         <is>
           <t>Undo used immediately after a placement.</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Second thoughts? Wise bees always double-check.</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>Re-charting the swarm!</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E96" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C97" s="1" t="inlineStr">
         <is>
-          <t>Re-charting the swarm!</t>
+          <t>Mid-air flight recalculation!</t>
         </is>
       </c>
       <c r="D97" s="1" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Mid-air flight recalculation!</t>
+          <t>Hovering backwards...</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C99" s="1" t="inlineStr">
         <is>
-          <t>Hovering backwards...</t>
+          <t>Plucking that card right back out of the wax.</t>
         </is>
       </c>
       <c r="D99" s="1" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Plucking that card right back out of the wax.</t>
+          <t>Unsticking that card from the comb.</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
@@ -3927,46 +3927,46 @@
       </c>
     </row>
     <row r="101" ht="14.6" customHeight="1" s="8">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>Undo used immediately after a placement.</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>Unsticking that card from the comb.</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Player wins a match with 4 rules active at once.</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>Four rules, one victory. Chaos bends to you.</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="102" ht="14.6" customHeight="1" s="8">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
-        <is>
-          <t>Player wins a match with 4 rules active at once.</t>
-        </is>
-      </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Four rules, one victory. Chaos bends to you.</t>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Opponent is winning by two cards and is about to place the last card on the board.</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>{OpponentName} prepares a final sting!</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Opponent is winning by two cards and is about to place the last card on the board.</t>
+          <t>Player flips 3+ cards in a single turn.</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>{OpponentName} prepares a final sting!</t>
+          <t>A massive swarm!</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -4015,12 +4015,12 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Player flips 3+ cards in a single turn.</t>
+          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>A massive swarm!</t>
+          <t>{OpponentName} unleashes an angry swarm!</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
+          <t>Combo x4 or higher.</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>{OpponentName} unleashes an angry swarm!</t>
+          <t>SWARM FRENZY — the whole hive is buzzing!</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Combo x4 or higher.</t>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>SWARM FRENZY — the whole hive is buzzing!</t>
+          <t>The hive is nearly overrun... is there any hope left?</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+          <t>A placed card captures on all 4 sides at once.</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>The hive is nearly overrun... is there any hope left?</t>
+          <t>Four-way sting!</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -4116,22 +4116,22 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>A placed card captures on all 4 sides at once.</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>Four-way sting!</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>{OpponentName} is starting to sweat.</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>Repeatable Flavor</t>
         </is>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>3+ rematch wins in a row against the same opponent.</t>
+          <t>3+ rematch losses in a row against the same opponent.</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>{OpponentName} is starting to sweat.</t>
+          <t>{OpponentName} has your number. Time for a new strategy?</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>3+ rematch losses in a row against the same opponent.</t>
+          <t>A 1-star card captures 3+ cards in one move.</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>{OpponentName} has your number. Time for a new strategy?</t>
+          <t>The weakest bee just took down half the hive!</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>A 1-star card captures 3+ cards in one move.</t>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>The weakest bee just took down half the hive!</t>
+          <t>A worker bee just humbled royalty.</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -4224,22 +4224,22 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
-        <is>
-          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
-        </is>
-      </c>
-      <c r="C112" s="5" t="inlineStr">
-        <is>
-          <t>A worker bee just humbled royalty.</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Second thoughts... wait, never mind, let's stick to the plan.</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
         <is>
           <t>Repeatable Flavor</t>
         </is>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Second thoughts... wait, never mind, let's stick to the plan.</t>
+          <t>A true rivalry is forming in the comb.</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+          <t>Player wins by the maximum possible margin.</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>A true rivalry is forming in the comb.</t>
+          <t>Nothing left to sting!</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -4307,25 +4307,25 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Player wins by the maximum possible margin.</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>Nothing left to sting!</t>
-        </is>
-      </c>
-      <c r="D115" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>First launch ever</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>A new bee joins the hive. Thank you for playing!</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -4339,12 +4339,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>First launch ever</t>
+          <t>Player reaches 10 total wins.</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>A new bee joins the hive. Thank you for playing!</t>
+          <t>10 wins. The hive takes notice.</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Player reaches 10 total wins.</t>
+          <t>Player reaches 100 total wins.</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>10 wins. The hive takes notice.</t>
+          <t>100 wins. The colony sings your name.</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Player reaches 100 total wins.</t>
+          <t>Player reaches 1000 total wins.</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>100 wins. The colony sings your name.</t>
+          <t>1000 wins. The hive bends to your will.</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -4415,22 +4415,22 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Milestones</t>
-        </is>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>Player reaches 1000 total wins.</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
-        <is>
-          <t>1000 wins. The hive bends to your will.</t>
-        </is>
-      </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Achievement</t>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Fallen Ace triggers (a '1' captures a '10').</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>The drone takes down the Queen!</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>The drone takes down the Queen!</t>
+          <t>A lucky sting! The mighty have fallen.</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -4467,27 +4467,27 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="A121" s="5" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Fallen Ace triggers (a '1' captures a '10').</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>A lucky sting! The mighty have fallen.</t>
-        </is>
-      </c>
-      <c r="D121" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>The pollen's thick today — {AscensionSuit} is in full bloom!</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -4501,12 +4501,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+          <t>Smoked Out drops a card's effective stat to 1.</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>The pollen's thick today — {AscensionSuit} is in full bloom!</t>
+          <t>Smoked out — that card can barely buzz anymore.</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -4521,56 +4521,56 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Smoked Out drops a card's effective stat to 1.</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>Smoked out — that card can barely buzz anymore.</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>The math checks out!</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="A124" s="5" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>The math checks out!</t>
-        </is>
-      </c>
-      <c r="D124" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>Toast</t>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>Player wins flawless (opponent score = 0).</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Flawless victory!</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>Win Banner</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>Flawless victory!</t>
+          <t>Hive domination!</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>Hive domination!</t>
+          <t>The colony reigns supreme..</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Player wins flawless (opponent score = 0).</t>
+          <t>Player loses flawless (0 captures).</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>The colony reigns supreme..</t>
+          <t>Every card fell. The hive lies in ruins.</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>Win Banner</t>
+          <t>You Lose Banner</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>Every card fell. The hive lies in ruins.</t>
+          <t>{OpponentName} didn't leave you a single card standing.</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>{OpponentName} didn't leave you a single card standing.</t>
+          <t>There are no bees left in your bonnet.</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -4715,14 +4715,14 @@
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>Player loses flawless (0 captures).</t>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>There are no bees left in your bonnet.</t>
+          <t>Pollen is in the air!</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>You Lose Banner</t>
+          <t>Game intro rules banner</t>
         </is>
       </c>
     </row>
@@ -4744,12 +4744,12 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Roulette rolls Pollination.</t>
+          <t>Roulette rolls Smoked Out.</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>Pollen is in the air!</t>
+          <t>A haze covers the comb!</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -4769,14 +4769,14 @@
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>Roulette rolls Smoked Out.</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>A haze covers the comb!</t>
+          <t>Addition is key!</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Math Bee</t>
+          <t>Roulette rolls Inversion</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Addition is key!</t>
+          <t>Everything is upside down!</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Inversion</t>
+          <t>Roulette rolls clear skies</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>Everything is upside down!</t>
+          <t>The hive is exposed!</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls clear skies</t>
+          <t>Roulette rolls scouting party</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>The hive is exposed!</t>
+          <t>The drones are out!</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls scouting party</t>
+          <t>Roulette rolls Frenzy</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>The drones are out!</t>
+          <t>Chaos takes over!</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Frenzy</t>
+          <t>Roulette rolls Symmetry</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Chaos takes over!</t>
+          <t>Patterns Align!</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Symmetry</t>
+          <t>Roulette rolls Nectar Exchange</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>Patterns Align!</t>
+          <t>A trade before the swarm!</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -4960,12 +4960,12 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Nectar Exchange</t>
+          <t>Roulette rolls Hierarchy</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>A trade before the swarm!</t>
+          <t>Order above all!</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -4980,324 +4980,297 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="inlineStr">
-        <is>
-          <t>Rule-Specific</t>
-        </is>
-      </c>
-      <c r="B140" s="5" t="inlineStr">
-        <is>
-          <t>Roulette rolls Hierarchy</t>
-        </is>
-      </c>
-      <c r="C140" s="5" t="inlineStr">
-        <is>
-          <t>Order above all!</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>Game intro rules banner</t>
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>Moonlight glints off the wax.</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Moonlight glints off the wax.</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>The dew hasn't dried and the bees are already at it.</t>
+        </is>
+      </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E141" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>The dew hasn't dried and the bees are already at it.</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B142" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>The hive hums with a fresh day's plans.</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E142" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>The hive hums with a fresh day's plans.</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B143" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="inlineStr">
+        <is>
+          <t>Even bees pause to enjoy the sunshine.</t>
+        </is>
+      </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E143" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="inlineStr">
         <is>
           <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Even bees pause to enjoy the sunshine.</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>Half the day's pollen is already in.</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E144" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Half the day's pollen is already in.</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B145" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>The hive settles into its afternoon rhythm.</t>
+        </is>
+      </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E145" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
         <is>
           <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>The hive settles into its afternoon rhythm.</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>Long shadows, long odds — let's play.</t>
+        </is>
+      </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Long shadows, long odds — let's play.</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>The last foragers are heading home.</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E147" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B148" s="1" t="inlineStr">
         <is>
           <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>The last foragers are heading home.</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>Lantern-bugs light the way to the hive.</t>
+        </is>
+      </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E148" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Lantern-bugs light the way to the hive.</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B149" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="inlineStr">
+        <is>
+          <t>The Queen's chambers go quiet, but not this table.</t>
+        </is>
+      </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E149" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
         <is>
           <t>Match starts between 9:00 PM and midnight local time.</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>The Queen's chambers go quiet, but not this table.</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Match starts between 9:00 PM and midnight local time.</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="C150" s="1" t="inlineStr">
         <is>
           <t>A nightcap of nectar before bed.</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -3777,7 +3777,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Second thoughts? Wise bees always double-check.</t>
+          <t>Wise bees always double-check.</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -4251,135 +4251,135 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Player plays against the same AI difficulty 5 times in a row.</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>A true rivalry is forming in the comb.</t>
-        </is>
-      </c>
-      <c r="D113" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>A worker bee never doubts their instincts... twice!</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" t="inlineStr">
         <is>
           <t>Gameplay</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>Player wins by the maximum possible margin.</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>Nothing left to sting!</t>
-        </is>
-      </c>
-      <c r="D114" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Just testing the Undo button, right?</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>Milestones</t>
-        </is>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>First launch ever</t>
-        </is>
-      </c>
-      <c r="C115" s="5" t="inlineStr">
-        <is>
-          <t>A new bee joins the hive. Thank you for playing!</t>
-        </is>
-      </c>
-      <c r="D115" s="7" t="inlineStr">
-        <is>
-          <t>Achievement</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>You just wanted to see that card flip again!</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>Milestones</t>
-        </is>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Player reaches 10 total wins.</t>
-        </is>
-      </c>
-      <c r="C116" s="5" t="inlineStr">
-        <is>
-          <t>10 wins. The hive takes notice.</t>
-        </is>
-      </c>
-      <c r="D116" s="7" t="inlineStr">
-        <is>
-          <t>Achievement</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>A plot twist... that went absolutely nowhere!</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>Milestones</t>
-        </is>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Player reaches 100 total wins.</t>
-        </is>
-      </c>
-      <c r="C117" s="5" t="inlineStr">
-        <is>
-          <t>100 wins. The colony sings your name.</t>
-        </is>
-      </c>
-      <c r="D117" s="7" t="inlineStr">
-        <is>
-          <t>Achievement</t>
-        </is>
-      </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Taking the scenic route to the exact same move!</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -4388,25 +4388,25 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Milestones</t>
-        </is>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>Player reaches 1000 total wins.</t>
-        </is>
-      </c>
-      <c r="C118" s="5" t="inlineStr">
-        <is>
-          <t>1000 wins. The hive bends to your will.</t>
-        </is>
-      </c>
-      <c r="D118" s="7" t="inlineStr">
-        <is>
-          <t>Achievement</t>
-        </is>
-      </c>
-      <c r="E118" s="7" t="inlineStr">
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>A true rivalry is forming in the comb.</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -4415,17 +4415,17 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Rule-Specific</t>
+          <t>Gameplay</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Fallen Ace triggers (a '1' captures a '10').</t>
+          <t>Player wins by the maximum possible margin.</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>The drone takes down the Queen!</t>
+          <t>Nothing left to sting!</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -4433,7 +4433,7 @@
           <t>Repeatable Flavor</t>
         </is>
       </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -4442,22 +4442,22 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Rule-Specific</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Fallen Ace triggers (a '1' captures a '10').</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>A lucky sting! The mighty have fallen.</t>
-        </is>
-      </c>
-      <c r="D120" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>First launch ever</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>A new bee joins the hive. Thank you for playing!</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>Achievement</t>
         </is>
       </c>
       <c r="E120" s="7" t="inlineStr">
@@ -4467,54 +4467,54 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="inlineStr">
-        <is>
-          <t>Rule-Specific</t>
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Milestones</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+          <t>Player reaches 10 total wins.</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>The pollen's thick today — {AscensionSuit} is in full bloom!</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
+          <t>10 wins. The hive takes notice.</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>Rule-Specific</t>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Milestones</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Smoked Out drops a card's effective stat to 1.</t>
+          <t>Player reaches 100 total wins.</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Smoked out — that card can barely buzz anymore.</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
+          <t>100 wins. The colony sings your name.</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -4523,81 +4523,81 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
+          <t>Milestones</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Player reaches 1000 total wins.</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>1000 wins. The hive bends to your will.</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>Achievement</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>The math checks out!</t>
-        </is>
-      </c>
-      <c r="D123" s="4" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Fallen Ace triggers (a '1' captures a '10').</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>The drone takes down the Queen!</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>Player wins flawless (opponent score = 0).</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>Flawless victory!</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>Win Banner</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="inlineStr">
-        <is>
-          <t>Rule-Specific</t>
-        </is>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>Player wins flawless (opponent score = 0).</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>Hive domination!</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>Win Banner</t>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>Fallen Ace triggers (a '1' captures a '10').</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>A lucky sting! The mighty have fallen.</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>Toast</t>
         </is>
       </c>
     </row>
@@ -4609,12 +4609,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Player wins flawless (opponent score = 0).</t>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>The colony reigns supreme..</t>
+          <t>The pollen's thick today — {AscensionSuit} is in full bloom!</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>Win Banner</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
@@ -4636,12 +4636,12 @@
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Player loses flawless (0 captures).</t>
+          <t>Smoked Out drops a card's effective stat to 1.</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>Every card fell. The hive lies in ruins.</t>
+          <t>Smoked out — that card can barely buzz anymore.</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>You Lose Banner</t>
+          <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>Player loses flawless (0 captures).</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>{OpponentName} didn't leave you a single card standing.</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>You Lose Banner</t>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>The math checks out!</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Toast</t>
         </is>
       </c>
     </row>
@@ -4690,12 +4690,12 @@
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Player loses flawless (0 captures).</t>
+          <t>Player wins flawless (opponent score = 0).</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>There are no bees left in your bonnet.</t>
+          <t>Flawless victory!</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>You Lose Banner</t>
+          <t>Win Banner</t>
         </is>
       </c>
     </row>
@@ -4715,14 +4715,14 @@
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>Roulette rolls Pollination.</t>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Player wins flawless (opponent score = 0).</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>Pollen is in the air!</t>
+          <t>Hive domination!</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>Game intro rules banner</t>
+          <t>Win Banner</t>
         </is>
       </c>
     </row>
@@ -4742,14 +4742,14 @@
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Roulette rolls Smoked Out.</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Player wins flawless (opponent score = 0).</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>A haze covers the comb!</t>
+          <t>The colony reigns supreme..</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>Game intro rules banner</t>
+          <t>Win Banner</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Math Bee</t>
+          <t>Player loses flawless (0 captures).</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>Addition is key!</t>
+          <t>Every card fell. The hive lies in ruins.</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>Game intro rules banner</t>
+          <t>You Lose Banner</t>
         </is>
       </c>
     </row>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Inversion</t>
+          <t>Player loses flawless (0 captures).</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>Everything is upside down!</t>
+          <t>{OpponentName} didn't leave you a single card standing.</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>Game intro rules banner</t>
+          <t>You Lose Banner</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls clear skies</t>
+          <t>Player loses flawless (0 captures).</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>The hive is exposed!</t>
+          <t>There are no bees left in your bonnet.</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>Game intro rules banner</t>
+          <t>You Lose Banner</t>
         </is>
       </c>
     </row>
@@ -4850,14 +4850,14 @@
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
-        <is>
-          <t>Roulette rolls scouting party</t>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>The drones are out!</t>
+          <t>Pollen is in the air!</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -4877,14 +4877,14 @@
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
-        <is>
-          <t>Roulette rolls Frenzy</t>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>Roulette rolls Smoked Out.</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>Chaos takes over!</t>
+          <t>A haze covers the comb!</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Symmetry</t>
+          <t>Roulette rolls Math Bee</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>Patterns Align!</t>
+          <t>Addition is key!</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Roulette rolls Nectar Exchange</t>
+          <t>Roulette rolls Inversion</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>A trade before the swarm!</t>
+          <t>Everything is upside down!</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -4960,157 +4960,157 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
+          <t>Roulette rolls clear skies</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>The hive is exposed!</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>The drones are out!</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Roulette rolls Frenzy</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Chaos takes over!</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Roulette rolls Symmetry</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Patterns Align!</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Roulette rolls Nectar Exchange</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>A trade before the swarm!</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
           <t>Roulette rolls Hierarchy</t>
         </is>
       </c>
-      <c r="C139" s="5" t="inlineStr">
+      <c r="C144" s="5" t="inlineStr">
         <is>
           <t>Order above all!</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
         <is>
           <t>Game intro rules banner</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>Moonlight glints off the wax.</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E140" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>The dew hasn't dried and the bees are already at it.</t>
-        </is>
-      </c>
-      <c r="D141" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E141" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B142" s="1" t="inlineStr">
-        <is>
-          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr">
-        <is>
-          <t>The hive hums with a fresh day's plans.</t>
-        </is>
-      </c>
-      <c r="D142" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E142" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B143" s="1" t="inlineStr">
-        <is>
-          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C143" s="1" t="inlineStr">
-        <is>
-          <t>Even bees pause to enjoy the sunshine.</t>
-        </is>
-      </c>
-      <c r="D143" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E143" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B144" s="1" t="inlineStr">
-        <is>
-          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr">
-        <is>
-          <t>Half the day's pollen is already in.</t>
-        </is>
-      </c>
-      <c r="D144" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E144" s="1" t="inlineStr">
-        <is>
-          <t>Loading</t>
         </is>
       </c>
     </row>
@@ -5122,12 +5122,12 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>The hive settles into its afternoon rhythm.</t>
+          <t>Moonlight glints off the wax.</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+          <t>Match starts between 5:00 AM and 8:00 AM local time.</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Long shadows, long odds — let's play.</t>
+          <t>The dew hasn't dried and the bees are already at it.</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+          <t>Match starts between 8:00 AM and 12:00 PM local time.</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>The last foragers are heading home.</t>
+          <t>The hive hums with a fresh day's plans.</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Lantern-bugs light the way to the hive.</t>
+          <t>Even bees pause to enjoy the sunshine.</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 9:00 PM and midnight local time.</t>
+          <t>Match starts between 12:00 PM and 2:00 PM local time.</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>The Queen's chambers go quiet, but not this table.</t>
+          <t>Half the day's pollen is already in.</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -5257,20 +5257,155 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>The hive settles into its afternoon rhythm.</t>
+        </is>
+      </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E150" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>Long shadows, long odds — let's play.</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E151" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>The last foragers are heading home.</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B153" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>Lantern-bugs light the way to the hive.</t>
+        </is>
+      </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E153" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B154" s="1" t="inlineStr">
+        <is>
           <t>Match starts between 9:00 PM and midnight local time.</t>
         </is>
       </c>
-      <c r="C150" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
+        <is>
+          <t>The Queen's chambers go quiet, but not this table.</t>
+        </is>
+      </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E154" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>Match starts between 9:00 PM and midnight local time.</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
         <is>
           <t>A nightcap of nectar before bed.</t>
         </is>
       </c>
-      <c r="D150" s="1" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E150" s="1" t="inlineStr">
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E155" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E225"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -4251,135 +4251,135 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
         <is>
           <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="1" t="inlineStr">
         <is>
           <t>A worker bee never doubts their instincts... twice!</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E113" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
         <is>
           <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="1" t="inlineStr">
         <is>
           <t>Just testing the Undo button, right?</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
         <is>
           <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="1" t="inlineStr">
         <is>
           <t>You just wanted to see that card flip again!</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
         <is>
           <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>A plot twist... that went absolutely nowhere!</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E116" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Gameplay</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
         <is>
           <t>Player uses Undo, thinks about it, and then makes the exact same move they just undid.</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="1" t="inlineStr">
         <is>
           <t>Taking the scenic route to the exact same move!</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
@@ -5408,6 +5408,1896 @@
       <c r="E155" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B156" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>Cornered in the comb... can you pull off a miracle?</t>
+        </is>
+      </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E156" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Down to your final stand! The hive needs a hero.</t>
+        </is>
+      </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E157" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>Only a few cells left! Can a single sting turn the tide?</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>Trapped in the comb... one last chance to strike back.</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>Well... this is getting uncomfortable.</t>
+        </is>
+      </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B161" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>Don't panic! ...Okay, maybe panic just a little.</t>
+        </is>
+      </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t>Player has only 2 cards on the board vs. opponent's 6, few spaces left.</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>Backed into a corner — just where we want 'em?</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>Player wins a match with 4 rules active at once.</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>The odds were quadrupled, and so was your glory!</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="inlineStr">
+        <is>
+          <t>Player wins a match with 4 rules active at once.</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>Four rules? Just four more reasons to win.</t>
+        </is>
+      </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E164" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>Sting 'em all!</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>Raking in the honey!</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B167" s="1" t="inlineStr">
+        <is>
+          <t>Player flips 3+ cards in a single turn.</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>A sweeping sting!</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E167" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B168" s="1" t="inlineStr">
+        <is>
+          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} shows no mercy!</t>
+        </is>
+      </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E168" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>Opponent flips 3+ of the player's cards in a single turn (not a Combo).</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} didn't hold back!</t>
+        </is>
+      </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B170" s="1" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="inlineStr">
+        <is>
+          <t>MEGA CASCADE — absolute hive pandemonium!</t>
+        </is>
+      </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t>HIVE SUPERNOVA — a four-fold combo explosion!</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>Combo x4 or higher.</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>ULTIMATE SWARM — cards flipping in every direction!</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Omnidirectional sting — nothing on that board was safe!</t>
+        </is>
+      </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E173" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B174" s="1" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="inlineStr">
+        <is>
+          <t>Royal center sting!</t>
+        </is>
+      </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E174" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B175" s="1" t="inlineStr">
+        <is>
+          <t>A placed card captures on all 4 sides at once.</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="inlineStr">
+        <is>
+          <t>Bullseye in the comb!</t>
+        </is>
+      </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B176" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName}'s wings are getting tired!</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} is losing their buzz!</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E177" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B178" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="inlineStr">
+        <is>
+          <t>You're ruling this hive!</t>
+        </is>
+      </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E178" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B179" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} can't catch a break.</t>
+        </is>
+      </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E179" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch wins in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} might need a quick coffee break.</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} is on a roll… time to shake up your deck!</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B182" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>Smoked out by {OpponentName} 3 times in a row!</t>
+        </is>
+      </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E182" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B183" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>The swarm is favoring {OpponentName}… for now!</t>
+        </is>
+      </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E183" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B184" s="1" t="inlineStr">
+        <is>
+          <t>3+ rematch losses in a row against the same opponent.</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>Got caught in {OpponentName}'s honey trap again!</t>
+        </is>
+      </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E184" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B185" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>A humble worker bee just staged a revolution!</t>
+        </is>
+      </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E185" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B186" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>Smallest bee, ENORMOUS sting!</t>
+        </is>
+      </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E186" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t>Don't judge a bee by its stars!</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E187" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures 3+ cards in one move.</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>Small card, big moves!</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>The ultimate rarity mismatch!</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>Rank means nothing to a sharp stinger!</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>Royalty is expensive — tactics are free!</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B192" s="1" t="inlineStr">
+        <is>
+          <t>A 1-star card captures a 5-star card (rarity mismatch).</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>Big stars fall hard!</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E192" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>Neither bee backs down — 5 matches and counting!</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E193" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B194" s="1" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="inlineStr">
+        <is>
+          <t>Five battles in the same comb! The bees are watching closely.</t>
+        </is>
+      </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B195" s="1" t="inlineStr">
+        <is>
+          <t>Player plays against the same AI difficulty 5 times in a row.</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>Deep in the hive, a classic matchup unfolds.</t>
+        </is>
+      </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>Absolute hive takeover!</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>All the honey is yours!</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
+        <is>
+          <t>Gameplay</t>
+        </is>
+      </c>
+      <c r="B198" s="1" t="inlineStr">
+        <is>
+          <t>Player wins by the maximum possible margin.</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr">
+        <is>
+          <t>Not even a drone left standing!</t>
+        </is>
+      </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B199" s="1" t="inlineStr">
+        <is>
+          <t>Nectar Exchange swaps away the player's 5-star card.</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="inlineStr">
+        <is>
+          <t>{OpponentName} just flew off with your Royal Jelly!</t>
+        </is>
+      </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B200" s="1" t="inlineStr">
+        <is>
+          <t>Nectar Exchange swaps away the player's 5-star card.</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="inlineStr">
+        <is>
+          <t>Highway robbery in the hive! {OpponentName} stole your 5-star!</t>
+        </is>
+      </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B201" s="1" t="inlineStr">
+        <is>
+          <t>Nectar Exchange trades the player's worst card for the opponent's best.</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="inlineStr">
+        <is>
+          <t>The nectar favors you.</t>
+        </is>
+      </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t>Nectar Exchange trades the player's worst card for the opponent's best.</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t>A golden exchange.</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>Pure, unadulterated honey — standard rules apply!</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B204" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="inlineStr">
+        <is>
+          <t>Back to basics for the bees!</t>
+        </is>
+      </c>
+      <c r="D204" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E204" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B205" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls zero extra rules.</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="inlineStr">
+        <is>
+          <t>Clean comb, clean rules — just you and the cards.</t>
+        </is>
+      </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E205" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t>Flowers are blooming!</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Pollination.</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t>Pollen. Everywhere.</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B208" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Smoked Out.</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="inlineStr">
+        <is>
+          <t>Smoke fills the hive…</t>
+        </is>
+      </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E208" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B209" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>Do the math!</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E209" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B210" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="inlineStr">
+        <is>
+          <t>Sum it up!</t>
+        </is>
+      </c>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E210" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B211" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>Calculate carefully!</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B212" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Math Bee</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>Class is in session!</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E212" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Inversion</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t>Flying backwards — low beats high!</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls clear skies</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t>Clear Skies overheard.</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B215" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls clear skies</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>No shade on the hive today.</t>
+        </is>
+      </c>
+      <c r="D215" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E215" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B216" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>Scout bees have reported back!</t>
+        </is>
+      </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E216" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B217" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>Reconnaissance in progress!</t>
+        </is>
+      </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E217" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B218" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls scouting party</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>Intel gathered!</t>
+        </is>
+      </c>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E218" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Frenzy</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>The bees are out of control!</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Frenzy</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>Those bees are wild!</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E220" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Symmetry</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>Geometric precision required.</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Nectar Exchange</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>Pre-game trading post open!</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B223" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Nectar Exchange</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>Nectar bartering begins!</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E223" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B224" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Hierarchy</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>Obey the Queen!</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E224" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B225" s="1" t="inlineStr">
+        <is>
+          <t>Roulette rolls Hierarchy</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>Royal decree issued!</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E225" s="1" t="inlineStr">
+        <is>
+          <t>Game intro rules banner</t>
         </is>
       </c>
     </row>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 12:00 AM and 4:00 AM local time.</t>
+          <t>Match starts between 12:00 AM and 5:00 AM local time.</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E225"/>
+  <dimension ref="A1:E250"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -7298,6 +7298,681 @@
       <c r="E225" s="1" t="inlineStr">
         <is>
           <t>Game intro rules banner</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B226" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>Hearts flutter through the hive today.</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E226" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B227" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>Every heart in the comb beats a little louder.</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E227" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B228" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr">
+        <is>
+          <t>The hive is full of hearts, and yours is winning.</t>
+        </is>
+      </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E228" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B229" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="inlineStr">
+        <is>
+          <t>Diamonds sparkle brighter on Valentine's Day.</t>
+        </is>
+      </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E229" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>The bees traded honey for diamonds today.</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>A diamond in the rough, sweeter than honey.</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B232" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="inlineStr">
+        <is>
+          <t>Clover and clubs bloom together this Valentine's.</t>
+        </is>
+      </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E232" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B233" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="inlineStr">
+        <is>
+          <t>Even the clubs are feeling the love today.</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E233" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B234" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="inlineStr">
+        <is>
+          <t>Cupid's arrow struck the spades first.</t>
+        </is>
+      </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E234" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B235" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="inlineStr">
+        <is>
+          <t>The spades soften their edges for Valentine's Day.</t>
+        </is>
+      </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E235" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B236" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Valentine's Day (Feb 14).</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="inlineStr">
+        <is>
+          <t>Even spades dig deep for love today.</t>
+        </is>
+      </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E236" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B237" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Earth Day (Apr 22).</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="inlineStr">
+        <is>
+          <t>Protect the flowers, save the bees! Happy Earth Day!</t>
+        </is>
+      </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E237" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B238" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on National Honey Day (Aug 15).</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="inlineStr">
+        <is>
+          <t>A golden celebration in the comb — Happy Honey Day!</t>
+        </is>
+      </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E238" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B239" s="1" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="inlineStr">
+        <is>
+          <t>Is that card really what it seems… or an April Fools' trick?</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E239" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B240" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Pi Day (Mar 14).</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="inlineStr">
+        <is>
+          <t>The math in the comb is extra precise today!</t>
+        </is>
+      </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E240" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B241" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on New Year's Eve (Dec 31).</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="inlineStr">
+        <is>
+          <t>Counting down the final buzz of the year!</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E241" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B242" s="1" t="inlineStr">
+        <is>
+          <t>Game loads on Christmas (Dec 25).</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="inlineStr">
+        <is>
+          <t>Peace, warmth, and sweetness to all in the hive this Christmas!</t>
+        </is>
+      </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E242" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B243" s="1" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="inlineStr">
+        <is>
+          <t>Is that a 5-star card, or just a worker bee in a fake crown?</t>
+        </is>
+      </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E243" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B244" s="1" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="inlineStr">
+        <is>
+          <t>Maybe it's time for a wasp theme…</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E244" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B245" s="1" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="inlineStr">
+        <is>
+          <t>Pranksters in the hive! Trust your cards, not the drones.</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E245" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Game loads on Holi.</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Vibrant colors bloom across the comb! Happy Holi!</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Game loads on Rosh Hashanah.</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Wishing you a sweet and fruitful new year — Shanah Tovah from the hive!</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Game loads on Diwali.</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Wishing you a season of light, sweetness, and harmony in the hive.</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Game loads on Eid al-Fitr.</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>A season of gratitude, sweetness, and joy. Eid Mubarak from the hive!</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Game loads on Hanukkah.</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>May your home bee filled with light, peace, and joy this Hanukkah.</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Loading</t>
         </is>
       </c>
     </row>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E250"/>
+  <dimension ref="A1:E258"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -7842,137 +7842,353 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B246" s="1" t="inlineStr">
         <is>
           <t>Game loads on Holi.</t>
         </is>
       </c>
-      <c r="C246" t="inlineStr">
+      <c r="C246" s="1" t="inlineStr">
         <is>
           <t>Vibrant colors bloom across the comb! Happy Holi!</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E246" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B247" s="1" t="inlineStr">
         <is>
           <t>Game loads on Rosh Hashanah.</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C247" s="1" t="inlineStr">
         <is>
           <t>Wishing you a sweet and fruitful new year — Shanah Tovah from the hive!</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E247" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B248" s="1" t="inlineStr">
         <is>
           <t>Game loads on Diwali.</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr">
+      <c r="C248" s="1" t="inlineStr">
         <is>
           <t>Wishing you a season of light, sweetness, and harmony in the hive.</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E248" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B249" s="1" t="inlineStr">
         <is>
           <t>Game loads on Eid al-Fitr.</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="1" t="inlineStr">
         <is>
           <t>A season of gratitude, sweetness, and joy. Eid Mubarak from the hive!</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E249" s="1" t="inlineStr">
         <is>
           <t>Loading</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>Loading</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
+      <c r="A250" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B250" s="1" t="inlineStr">
         <is>
           <t>Game loads on Hanukkah.</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C250" s="1" t="inlineStr">
         <is>
           <t>May your home bee filled with light, peace, and joy this Hanukkah.</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>Loading</t>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E250" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+      <c r="B251" s="1" t="inlineStr">
+        <is>
+          <t>Playing on April Fools' Day (Apr 1).</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="inlineStr">
+        <is>
+          <t>Is that diamond or a rhinestone?</t>
+        </is>
+      </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E251" s="1" t="inlineStr">
+        <is>
+          <t>Loading</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Calculating 475 moves ahead, or taking a snack break?</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>The cards aren't going to play themselves… though that would be a neat.</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Checking your hand twice? Santa Bee would be proud.</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>No pressure, it's only the entire match on the line.</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>A masterclass in the dramatic pause.</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Shuffling your thoughts? We've got time.</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Brain.exe is processing the optimal placement…</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Toast</t>
         </is>
       </c>
     </row>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E258"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -4452,7 +4452,7 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>A new bee joins the hive. Thank you for playing!</t>
+          <t>Welcome to the colony! Time to make some honey.</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>1000 wins. The hive bends to your will.</t>
+          <t>1000 wins. A millennium of triumph. The Queen herself applauds.</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -8004,189 +8004,297 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
+      <c r="C252" s="1" t="inlineStr">
         <is>
           <t>Calculating 475 moves ahead, or taking a snack break?</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D252" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E252" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
+      <c r="C253" s="1" t="inlineStr">
         <is>
           <t>The cards aren't going to play themselves… though that would be a neat.</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
+      <c r="D253" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
+      <c r="C254" s="1" t="inlineStr">
         <is>
           <t>Checking your hand twice? Santa Bee would be proud.</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
+      <c r="D254" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E254" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
+      <c r="C255" s="1" t="inlineStr">
         <is>
           <t>No pressure, it's only the entire match on the line.</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
+      <c r="D255" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
+      <c r="C256" s="1" t="inlineStr">
         <is>
           <t>A masterclass in the dramatic pause.</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
+      <c r="D256" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
+      <c r="C257" s="1" t="inlineStr">
         <is>
           <t>Shuffling your thoughts? We've got time.</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
+      <c r="D257" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="1" t="inlineStr">
         <is>
           <t>Idle Action</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="1" t="inlineStr">
         <is>
           <t>No action taken for one minute.</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
+      <c r="C258" s="1" t="inlineStr">
         <is>
           <t>Brain.exe is processing the optimal placement…</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
+      <c r="D258" s="1" t="inlineStr">
         <is>
           <t>Ambiance</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Calculated to perfection!</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>{AscensionSuit} is drowning in nectar!</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Pollination pushes a card's modifier to +3 or higher.</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>A massive harvest! {AscensionSuit} thrives.</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Rule-Specific</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Smoked Out drops a card's effective stat to 1.</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Lethargic and grounded.</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -5284,7 +5284,7 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Match starts between 2:00 PM and 5:00 PM local time.</t>
+          <t>Match starts between 5:00 PM and 9:00 PM local time.</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
@@ -8193,108 +8193,108 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="1" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="1" t="inlineStr">
         <is>
           <t>A player triggers a "Plus" combo (the math matches perfectly).</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
+      <c r="C259" s="1" t="inlineStr">
         <is>
           <t>Calculated to perfection!</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E259" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="1" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="1" t="inlineStr">
         <is>
           <t>Pollination pushes a card's modifier to +3 or higher.</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
+      <c r="C260" s="1" t="inlineStr">
         <is>
           <t>{AscensionSuit} is drowning in nectar!</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E260" t="inlineStr">
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E260" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="1" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="1" t="inlineStr">
         <is>
           <t>Pollination pushes a card's modifier to +3 or higher.</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
+      <c r="C261" s="1" t="inlineStr">
         <is>
           <t>A massive harvest! {AscensionSuit} thrives.</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E261" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="1" t="inlineStr">
         <is>
           <t>Rule-Specific</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="1" t="inlineStr">
         <is>
           <t>Smoked Out drops a card's effective stat to 1.</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
+      <c r="C262" s="1" t="inlineStr">
         <is>
           <t>Lethargic and grounded.</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Repeatable Flavor</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>Repeatable Flavor</t>
+        </is>
+      </c>
+      <c r="E262" s="1" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>

--- a/tools/Honeycomb_Fun_Messages.xlsx
+++ b/tools/Honeycomb_Fun_Messages.xlsx
@@ -1216,7 +1216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E262"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="21.3516" customWidth="1" style="1" min="1" max="1"/>
@@ -8295,6 +8295,708 @@
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Has science gone too far? Click here to see this 10-star card.</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Local worker bee discovers secret to endless nectar...</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Top 10 cards to steal from the Queen. Number 4 will sting you!</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Beekeepers will hate you! Win every match with this one simple trick!</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Get rich or buzz trying.</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>To bee, or not to bee... wait, whose turn is it?</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>May the swarm be with you.</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Live, Laugh, Pollinate.</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Keep calm and buzz on.</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Home is where the hive is.</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Just a worker bee looking for my queen.</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Are you gonna play a card, or just sit there looking sweet?</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Frankly, my dear, I don't give a buzz.</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>We're gonna need a bigger hive.</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Show me the honey!</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>I'll bee back.</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Nobody puts Baby Bee in a corner.</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Sweet dreams are made of bees.</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Bee yourself; everyone else is already taken.</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Mind your own beeswax!</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>This one weird trick captures 4 cards at once — dealers don't want you to know it.</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>You won't believe what happened when a worker bee met a Fallen Ace.</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>She said yes to Symmetry. He said yes to Math Bee. Chaos ensued.</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Busy as a bee, broke as a beekeeper.</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Absence makes the heart grow fonder — and the hive grow louder.</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Idle Action</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>No action taken for one minute.</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Two bees or not two bees — that's a math problem, not a question.</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Ambiance</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
